--- a/DesignData/Excel_Masters/Stage/StageStats_Master.xlsx
+++ b/DesignData/Excel_Masters/Stage/StageStats_Master.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unreal\ProjectParadise\DesignData\Excel_Masters\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DAAEEC-67E3-469A-8BC9-9BEA9CE9298D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10035"/>
+    <workbookView xWindow="5100" yWindow="330" windowWidth="22290" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StageStats" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="110">
   <si>
     <t>---</t>
   </si>
@@ -346,12 +347,15 @@
   </si>
   <si>
     <t>.--.  .-  .-.  .-  -..  ..  ...  .</t>
+  </si>
+  <si>
+    <t>HomeBaseHPMultiplier</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1262,11 +1266,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1277,25 +1281,28 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1306,25 +1313,28 @@
         <v>90</v>
       </c>
       <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>100</v>
       </c>
-      <c r="E2">
-        <v>1000</v>
-      </c>
       <c r="F2">
+        <v>1000</v>
+      </c>
+      <c r="G2">
         <v>50</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>59</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1335,25 +1345,28 @@
         <v>90</v>
       </c>
       <c r="D3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E3">
         <v>120</v>
       </c>
-      <c r="E3">
-        <v>1000</v>
-      </c>
       <c r="F3">
+        <v>1000</v>
+      </c>
+      <c r="G3">
         <v>60</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>60</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1364,25 +1377,28 @@
         <v>90</v>
       </c>
       <c r="D4">
+        <v>1.21</v>
+      </c>
+      <c r="E4">
         <v>140</v>
       </c>
-      <c r="E4">
-        <v>1000</v>
-      </c>
       <c r="F4">
+        <v>1000</v>
+      </c>
+      <c r="G4">
         <v>70</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>15</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>61</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1393,25 +1409,28 @@
         <v>90</v>
       </c>
       <c r="D5">
+        <v>1.331</v>
+      </c>
+      <c r="E5">
         <v>160</v>
       </c>
-      <c r="E5">
-        <v>1000</v>
-      </c>
       <c r="F5">
+        <v>1000</v>
+      </c>
+      <c r="G5">
         <v>80</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>17</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>62</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1422,25 +1441,28 @@
         <v>120</v>
       </c>
       <c r="D6">
+        <v>1.4641</v>
+      </c>
+      <c r="E6">
         <v>300</v>
       </c>
-      <c r="E6">
-        <v>1000</v>
-      </c>
       <c r="F6">
+        <v>1000</v>
+      </c>
+      <c r="G6">
         <v>150</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>19</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>63</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1451,25 +1473,28 @@
         <v>90</v>
       </c>
       <c r="D7">
+        <v>1.6105100000000001</v>
+      </c>
+      <c r="E7">
         <v>260</v>
       </c>
-      <c r="E7">
-        <v>1000</v>
-      </c>
       <c r="F7">
+        <v>1000</v>
+      </c>
+      <c r="G7">
         <v>130</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>21</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>64</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1480,25 +1505,28 @@
         <v>90</v>
       </c>
       <c r="D8">
+        <v>1.7715609999999999</v>
+      </c>
+      <c r="E8">
         <v>280</v>
       </c>
-      <c r="E8">
-        <v>1000</v>
-      </c>
       <c r="F8">
+        <v>1000</v>
+      </c>
+      <c r="G8">
         <v>140</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>23</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>65</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1509,25 +1537,28 @@
         <v>90</v>
       </c>
       <c r="D9">
+        <v>1.9487171000000001</v>
+      </c>
+      <c r="E9">
         <v>300</v>
       </c>
-      <c r="E9">
-        <v>1000</v>
-      </c>
       <c r="F9">
+        <v>1000</v>
+      </c>
+      <c r="G9">
         <v>150</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>25</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>66</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1538,25 +1569,28 @@
         <v>120</v>
       </c>
       <c r="D10">
+        <v>2.1435888099999998</v>
+      </c>
+      <c r="E10">
         <v>500</v>
       </c>
-      <c r="E10">
-        <v>1000</v>
-      </c>
       <c r="F10">
+        <v>1000</v>
+      </c>
+      <c r="G10">
         <v>250</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>28</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>67</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1567,25 +1601,28 @@
         <v>90</v>
       </c>
       <c r="D11">
+        <v>2.3579476910000001</v>
+      </c>
+      <c r="E11">
         <v>320</v>
       </c>
-      <c r="E11">
-        <v>1000</v>
-      </c>
       <c r="F11">
+        <v>1000</v>
+      </c>
+      <c r="G11">
         <v>160</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>68</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1596,25 +1633,28 @@
         <v>90</v>
       </c>
       <c r="D12">
+        <v>2.5937424600000001</v>
+      </c>
+      <c r="E12">
         <v>180</v>
       </c>
-      <c r="E12">
-        <v>1000</v>
-      </c>
       <c r="F12">
+        <v>1000</v>
+      </c>
+      <c r="G12">
         <v>90</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>31</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>69</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1625,25 +1665,28 @@
         <v>90</v>
       </c>
       <c r="D13">
+        <v>2.8531167059999998</v>
+      </c>
+      <c r="E13">
         <v>200</v>
       </c>
-      <c r="E13">
-        <v>1000</v>
-      </c>
       <c r="F13">
+        <v>1000</v>
+      </c>
+      <c r="G13">
         <v>100</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>33</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>70</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1654,25 +1697,28 @@
         <v>90</v>
       </c>
       <c r="D14">
+        <v>3.1384283769999999</v>
+      </c>
+      <c r="E14">
         <v>220</v>
       </c>
-      <c r="E14">
-        <v>1000</v>
-      </c>
       <c r="F14">
+        <v>1000</v>
+      </c>
+      <c r="G14">
         <v>110</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>35</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>71</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1683,25 +1729,28 @@
         <v>90</v>
       </c>
       <c r="D15">
+        <v>3.452271214</v>
+      </c>
+      <c r="E15">
         <v>240</v>
       </c>
-      <c r="E15">
-        <v>1000</v>
-      </c>
       <c r="F15">
+        <v>1000</v>
+      </c>
+      <c r="G15">
         <v>120</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>37</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>72</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1712,25 +1761,28 @@
         <v>180</v>
       </c>
       <c r="D16">
+        <v>3.7974983359999999</v>
+      </c>
+      <c r="E16">
         <v>600</v>
       </c>
-      <c r="E16">
-        <v>1000</v>
-      </c>
       <c r="F16">
+        <v>1000</v>
+      </c>
+      <c r="G16">
         <v>300</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>39</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>73</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1741,25 +1793,28 @@
         <v>90</v>
       </c>
       <c r="D17">
+        <v>4.1772481690000003</v>
+      </c>
+      <c r="E17">
         <v>340</v>
       </c>
-      <c r="E17">
-        <v>1000</v>
-      </c>
       <c r="F17">
+        <v>1000</v>
+      </c>
+      <c r="G17">
         <v>170</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>41</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>74</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1770,25 +1825,28 @@
         <v>90</v>
       </c>
       <c r="D18">
+        <v>4.5949729860000001</v>
+      </c>
+      <c r="E18">
         <v>360</v>
       </c>
-      <c r="E18">
-        <v>1000</v>
-      </c>
       <c r="F18">
+        <v>1000</v>
+      </c>
+      <c r="G18">
         <v>180</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>43</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>75</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1799,25 +1857,28 @@
         <v>90</v>
       </c>
       <c r="D19">
+        <v>5.0544702849999998</v>
+      </c>
+      <c r="E19">
         <v>380</v>
       </c>
-      <c r="E19">
-        <v>1000</v>
-      </c>
       <c r="F19">
+        <v>1000</v>
+      </c>
+      <c r="G19">
         <v>190</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>45</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>76</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1828,25 +1889,28 @@
         <v>90</v>
       </c>
       <c r="D20">
+        <v>5.5599173129999997</v>
+      </c>
+      <c r="E20">
         <v>400</v>
       </c>
-      <c r="E20">
-        <v>1000</v>
-      </c>
       <c r="F20">
+        <v>1000</v>
+      </c>
+      <c r="G20">
         <v>200</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>47</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>77</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -1857,25 +1921,28 @@
         <v>180</v>
       </c>
       <c r="D21">
-        <v>1000</v>
+        <v>6.1159090450000004</v>
       </c>
       <c r="E21">
         <v>1000</v>
       </c>
       <c r="F21">
+        <v>1000</v>
+      </c>
+      <c r="G21">
         <v>500</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>49</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>78</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -1886,25 +1953,28 @@
         <v>180</v>
       </c>
       <c r="D22">
-        <v>1000</v>
+        <v>6.7274999490000003</v>
       </c>
       <c r="E22">
         <v>1000</v>
       </c>
       <c r="F22">
+        <v>1000</v>
+      </c>
+      <c r="G22">
         <v>500</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>51</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>79</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1915,25 +1985,28 @@
         <v>180</v>
       </c>
       <c r="D23">
-        <v>1000</v>
+        <v>7.4002499439999996</v>
       </c>
       <c r="E23">
         <v>1000</v>
       </c>
       <c r="F23">
+        <v>1000</v>
+      </c>
+      <c r="G23">
         <v>500</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>53</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>80</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1944,25 +2017,28 @@
         <v>180</v>
       </c>
       <c r="D24">
-        <v>1000</v>
+        <v>8.1402749389999993</v>
       </c>
       <c r="E24">
         <v>1000</v>
       </c>
       <c r="F24">
+        <v>1000</v>
+      </c>
+      <c r="G24">
         <v>500</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>55</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>81</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -1973,25 +2049,28 @@
         <v>180</v>
       </c>
       <c r="D25">
-        <v>1000</v>
+        <v>8.9543024330000005</v>
       </c>
       <c r="E25">
         <v>1000</v>
       </c>
       <c r="F25">
+        <v>1000</v>
+      </c>
+      <c r="G25">
         <v>500</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>57</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>82</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>56</v>
       </c>
@@ -2002,21 +2081,24 @@
         <v>180</v>
       </c>
       <c r="D26">
-        <v>1000</v>
+        <v>9.8497326760000004</v>
       </c>
       <c r="E26">
         <v>1000</v>
       </c>
       <c r="F26">
+        <v>1000</v>
+      </c>
+      <c r="G26">
         <v>500</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>58</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>83</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>108</v>
       </c>
     </row>

--- a/DesignData/Excel_Masters/Stage/StageStats_Master.xlsx
+++ b/DesignData/Excel_Masters/Stage/StageStats_Master.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unreal\ProjectParadise\DesignData\Excel_Masters\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\megabonk\Paradise\ProjectParadise\DesignData\Excel_Masters\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DAAEEC-67E3-469A-8BC9-9BEA9CE9298D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="330" windowWidth="22290" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5100" yWindow="330" windowWidth="22290" windowHeight="13635"/>
   </bookViews>
   <sheets>
     <sheet name="StageStats" sheetId="1" r:id="rId1"/>
@@ -355,7 +354,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1266,7 +1265,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1310,7 +1309,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1342,7 +1341,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D3">
         <v>1.1000000000000001</v>
@@ -1374,7 +1373,7 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D4">
         <v>1.21</v>
@@ -1406,7 +1405,7 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D5">
         <v>1.331</v>
@@ -1438,7 +1437,7 @@
         <v>18</v>
       </c>
       <c r="C6">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D6">
         <v>1.4641</v>
@@ -1470,7 +1469,7 @@
         <v>20</v>
       </c>
       <c r="C7">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D7">
         <v>1.6105100000000001</v>
@@ -1502,7 +1501,7 @@
         <v>22</v>
       </c>
       <c r="C8">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D8">
         <v>1.7715609999999999</v>
@@ -1534,7 +1533,7 @@
         <v>24</v>
       </c>
       <c r="C9">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D9">
         <v>1.9487171000000001</v>
@@ -1566,7 +1565,7 @@
         <v>27</v>
       </c>
       <c r="C10">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D10">
         <v>2.1435888099999998</v>
@@ -1598,7 +1597,7 @@
         <v>26</v>
       </c>
       <c r="C11">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D11">
         <v>2.3579476910000001</v>
@@ -1630,7 +1629,7 @@
         <v>30</v>
       </c>
       <c r="C12">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D12">
         <v>2.5937424600000001</v>
@@ -1662,7 +1661,7 @@
         <v>32</v>
       </c>
       <c r="C13">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D13">
         <v>2.8531167059999998</v>
@@ -1694,7 +1693,7 @@
         <v>34</v>
       </c>
       <c r="C14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D14">
         <v>3.1384283769999999</v>
@@ -1726,7 +1725,7 @@
         <v>36</v>
       </c>
       <c r="C15">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D15">
         <v>3.452271214</v>
@@ -1758,7 +1757,7 @@
         <v>38</v>
       </c>
       <c r="C16">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="D16">
         <v>3.7974983359999999</v>
@@ -1790,7 +1789,7 @@
         <v>40</v>
       </c>
       <c r="C17">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D17">
         <v>4.1772481690000003</v>
@@ -1822,7 +1821,7 @@
         <v>42</v>
       </c>
       <c r="C18">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D18">
         <v>4.5949729860000001</v>
@@ -1854,7 +1853,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D19">
         <v>5.0544702849999998</v>
@@ -1886,7 +1885,7 @@
         <v>46</v>
       </c>
       <c r="C20">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D20">
         <v>5.5599173129999997</v>
@@ -1918,7 +1917,7 @@
         <v>48</v>
       </c>
       <c r="C21">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="D21">
         <v>6.1159090450000004</v>
@@ -1950,7 +1949,7 @@
         <v>50</v>
       </c>
       <c r="C22">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="D22">
         <v>6.7274999490000003</v>
@@ -1982,7 +1981,7 @@
         <v>52</v>
       </c>
       <c r="C23">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="D23">
         <v>7.4002499439999996</v>
@@ -2014,7 +2013,7 @@
         <v>54</v>
       </c>
       <c r="C24">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="D24">
         <v>8.1402749389999993</v>
@@ -2046,7 +2045,7 @@
         <v>56</v>
       </c>
       <c r="C25">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="D25">
         <v>8.9543024330000005</v>
@@ -2078,7 +2077,7 @@
         <v>56</v>
       </c>
       <c r="C26">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="D26">
         <v>9.8497326760000004</v>
@@ -2105,5 +2104,6 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>